--- a/excel/硅.xlsx
+++ b/excel/硅.xlsx
@@ -664,10 +664,8 @@
         <f>IF(AND(ISNUMBER(T2),ISNUMBER(N2),N2&lt;&gt;0),(T2-N2)/N2,"-")</f>
         <v/>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V2" t="n">
+        <v>41.07</v>
       </c>
       <c r="W2">
         <f>IF(AND(ISNUMBER(V2),ISNUMBER(O2),O2&lt;&gt;0),(V2-O2)/O2,"-")</f>
@@ -675,7 +673,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2025 主动减产挺价（-22.3%）；2026Q1 检修压产、毛利率回升至 19%</t>
+          <t>2025 主动减产挺价（-22.3%）；2026Q1 检修压产、毛利率回升至 19%；26Q2 季度经营数据公告约 8 月底披露（截至 2026-08-23 未发布）</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -685,7 +683,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>季度经营数据公告产量口径（含自用，与年报口径或有差异）；24/25 年度=年报值，季度值平台拟合（斜体）；26Q1=39.67 万吨为 2026-04-30 季度经营数据公告实际值；2023 年度及各季待回填</t>
+          <t>季度经营数据公告产量口径（含自用，与年报口径或有差异）；24/25 年度=年报值，季度值平台拟合（斜体）；26Q1=39.67 万吨为 2026-04-30 季度经营数据公告实际值；2023 年度及各季待回填；26Q2 待 2026 半年报/季度经营数据公告披露（约 8 月底）；2026Q2经营数据公告(8/25)：工业硅生产量410,686.71吨=41.07万吨（单季口径，销量30.20万吨）</t>
         </is>
       </c>
     </row>
@@ -804,7 +802,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026中报(8/24)未披露工业硅产量；经营数据公告仅有机硅基础产品Q2产71,818吨(非工业硅口径)</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -933,7 +931,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026中报(8/24)未披露工业硅产量(金属硅为外购原料,H1均价8,101.61元/吨)；有机硅系列H1产17.31万吨(非工业硅)</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1062,7 +1060,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026中报(8/19)无任何产量披露(仅产能60万吨有机硅单体/年+分产品营收)</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1429,19 +1427,15 @@
         <f>IF(AND(ISNUMBER(R8),ISNUMBER(M8),M8&lt;&gt;0),(R8-M8)/M8,"-")</f>
         <v/>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T8" t="n">
+        <v>9.5</v>
       </c>
       <c r="U8">
         <f>IF(AND(ISNUMBER(T8),ISNUMBER(N8),N8&lt;&gt;0),(T8-N8)/N8,"-")</f>
         <v/>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V8" t="n">
+        <v>9.6</v>
       </c>
       <c r="W8">
         <f>IF(AND(ISNUMBER(V8),ISNUMBER(O8),O8&lt;&gt;0),(V8-O8)/O8,"-")</f>
@@ -1449,7 +1443,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Silicon Products 分部销量口径（kt，Excl. microsilica/quartz）；2026-02 Silicones 分部出售给 Bluestar，2026 起仅 Silicon Products 分部</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1459,7 +1453,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>销量口径（sales volumes），非生产量；季度序列待回填</t>
+          <t>销量口径（sales volumes，非生产量）；2026 起 Silicones 已剥离，硅口径=Silicon Products 分部；26Q1=95kt（H1 191kt−Q2 96kt 推算）、26Q2=96kt（kt÷10=万吨）；源 Elkem 2Q2026 报告 Key Figures</t>
         </is>
       </c>
     </row>
@@ -2461,27 +2455,33 @@
         <f>IF(AND(ISNUMBER(R16),ISNUMBER(M16),M16&lt;&gt;0),(R16-M16)/M16,"-")</f>
         <v/>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T16" t="n">
+        <v>9.119999999999999</v>
       </c>
       <c r="U16">
         <f>IF(AND(ISNUMBER(T16),ISNUMBER(N16),N16&lt;&gt;0),(T16-N16)/N16,"-")</f>
         <v/>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V16" t="n">
+        <v>10.37</v>
       </c>
       <c r="W16">
         <f>IF(AND(ISNUMBER(V16),ISNUMBER(O16),O16&lt;&gt;0),(V16-O16)/O16,"-")</f>
         <v/>
       </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>发货量口径（非产量）=硅金属+硅铁合计；硅金属 26Q1 30,533 / 26Q2 40,818 MT，硅铁 26Q1 60,674 / 26Q2 62,915 MT</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>季报≈季后4-5周；补海外工业硅缺口；发货量与产量口径差异需单独标注；2026-08-18新增骨架行，数据待回填</t>
+          <t>发货量口径（shipments，非产量），与产量口径差异需注意；MT÷10000=万吨；源 Ferroglobe Q2 2026 业绩新闻稿(2026-08-04) Product Category 表</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="U21">
@@ -4767,16 +4767,26 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="W21">
         <f>IF(AND(ISNUMBER(V21),ISNUMBER(O21),O21&lt;&gt;0),(V21-O21)/O21,"-")</f>
         <v/>
       </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>OCI 季度 IR 仅披露产能(35kMT/年)+开工率(Q1 15 个月法定检修降负荷、Q2 ~90%)，未披露分季度产量吨数</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>季度资料库（≈季后4-6周）；补海外多晶硅缺口；2026-08-18新增骨架行，数据待回填</t>
+          <t>季度资料库（≈季后4-6周）；补海外多晶硅缺口；2026-08-18新增骨架行，数据待回填；26Q1/Q2 分季度产量吨数未在 IR 官网披露（仅产能 35kMT/年+开工率），DART 事业报告 생산실적 待人工核查</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4942,6 +4952,40 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>补录 26Q1/26Q2：Elkem 硅销量(Silicon Products)26Q1=9.5/26Q2=9.6万吨（Silicones 已剥离，口径=Silicon Products）；Ferroglobe 发货量(硅金属+硅铁)26Q1=9.12/26Q2=10.37万吨；OCI 26Q1/26Q2 未披露分季产量吨数→标"未找到"；合盛 26Q2→标"待披露"(约8月底经营数据公告)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Elkem 2Q2026 报告 Key Figures；Ferroglobe 2026-08-04 业绩新闻稿；OCI Holdings Q1/Q2 2026 IR Presentation；合盛硅业 2026-07-14 半年度业绩预告</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>硅 26Q2 中报核查：新安/兴发/东岳中报均未披露工业硅产量（标'未披露'；新安/兴发有有机硅口径产量可作有机硅板块参考）</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>三公司2026中报+经营数据公告（巨潮/上交所 8/19-8/24）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel/硅.xlsx
+++ b/excel/硅.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:AB17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -550,17 +550,27 @@
           <t>26Q2同比</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>26Q3</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>26Q3同比</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>变化原因</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>FY2026指引</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -671,17 +681,17 @@
         <f>IF(AND(ISNUMBER(V2),ISNUMBER(O2),O2&lt;&gt;0),(V2-O2)/O2,"-")</f>
         <v/>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>2025 主动减产挺价（-22.3%）；2026Q1 检修压产、毛利率回升至 19%；26Q2 季度经营数据公告约 8 月底披露（截至 2026-08-23 未发布）</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>季度经营数据公告产量口径（含自用，与年报口径或有差异）；24/25 年度=年报值，季度值平台拟合（斜体）；26Q1=39.67 万吨为 2026-04-30 季度经营数据公告实际值；2023 年度及各季待回填；26Q2 待 2026 半年报/季度经营数据公告披露（约 8 月底）；2026Q2经营数据公告(8/25)：工业硅生产量410,686.71吨=41.07万吨（单季口径，销量30.20万吨）</t>
         </is>
@@ -800,17 +810,17 @@
         <f>IF(AND(ISNUMBER(V3),ISNUMBER(O3),O3&lt;&gt;0),(V3-O3)/O3,"-")</f>
         <v/>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>2026中报(8/24)未披露工业硅产量；经营数据公告仅有机硅基础产品Q2产71,818吨(非工业硅口径)</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>产量序列待回填（年报/中报口径）；'-'=待核，勿当零</t>
         </is>
@@ -929,17 +939,17 @@
         <f>IF(AND(ISNUMBER(V4),ISNUMBER(O4),O4&lt;&gt;0),(V4-O4)/O4,"-")</f>
         <v/>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>2026中报(8/24)未披露工业硅产量(金属硅为外购原料,H1均价8,101.61元/吨)；有机硅系列H1产17.31万吨(非工业硅)</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>产量序列待回填（年报/中报口径）；'-'=待核，勿当零</t>
         </is>
@@ -1058,17 +1068,17 @@
         <f>IF(AND(ISNUMBER(V5),ISNUMBER(O5),O5&lt;&gt;0),(V5-O5)/O5,"-")</f>
         <v/>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>2026中报(8/19)无任何产量披露(仅产能60万吨有机硅单体/年+分产品营收)</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>产量序列待回填（年报/中报口径）；'-'=待核，勿当零</t>
         </is>
@@ -1187,17 +1197,17 @@
         <f>IF(AND(ISNUMBER(V6),ISNUMBER(O6),O6&lt;&gt;0),(V6-O6)/O6,"-")</f>
         <v/>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2026-07 调研：17 台 33MVA 炉开 12 台，月产 2 万+吨</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>调研口径（2026-07 新疆调研）：满产约 3 万吨/月，完全成本约 8,300 元/吨为市场最低；年度序列待回填</t>
         </is>
@@ -1316,17 +1326,17 @@
         <f>IF(AND(ISNUMBER(V7),ISNUMBER(O7),O7&lt;&gt;0),(V7-O7)/O7,"-")</f>
         <v/>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>季度序列待回填（铁合金在线/百川口径）；'-'=待核，勿当零</t>
         </is>
@@ -1441,17 +1451,17 @@
         <f>IF(AND(ISNUMBER(V8),ISNUMBER(O8),O8&lt;&gt;0),(V8-O8)/O8,"-")</f>
         <v/>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>Silicon Products 分部销量口径（kt，Excl. microsilica/quartz）；2026-02 Silicones 分部出售给 Bluestar，2026 起仅 Silicon Products 分部</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>销量口径（sales volumes，非生产量）；2026 起 Silicones 已剥离，硅口径=Silicon Products 分部；26Q1=95kt（H1 191kt−Q2 96kt 推算）、26Q2=96kt（kt÷10=万吨）；源 Elkem 2Q2026 报告 Key Figures</t>
         </is>
@@ -1570,17 +1580,17 @@
         <f>IF(AND(ISNUMBER(V9),ISNUMBER(O9),O9&lt;&gt;0),(V9-O9)/O9,"-")</f>
         <v/>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>配套多晶硅一体化放量（计划）</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>产量序列待回填；'-'=待核，勿当零</t>
         </is>
@@ -1699,17 +1709,17 @@
         <f>IF(AND(ISNUMBER(V10),ISNUMBER(O10),O10&lt;&gt;0),(V10-O10)/O10,"-")</f>
         <v/>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>产能锚点占位；多晶硅产量见多晶硅板块</t>
         </is>
@@ -1828,17 +1838,17 @@
         <f>IF(AND(ISNUMBER(V11),ISNUMBER(O11),O11&lt;&gt;0),(V11-O11)/O11,"-")</f>
         <v/>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>产能锚点占位，尚无产量披露</t>
         </is>
@@ -1957,17 +1967,17 @@
         <f>IF(AND(ISNUMBER(V12),ISNUMBER(O12),O12&lt;&gt;0),(V12-O12)/O12,"-")</f>
         <v/>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>产能锚点占位；多晶硅产量见多晶硅板块</t>
         </is>
@@ -2086,17 +2096,17 @@
         <f>IF(AND(ISNUMBER(V13),ISNUMBER(O13),O13&lt;&gt;0),(V13-O13)/O13,"-")</f>
         <v/>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>2026 逐步投产（配套新特多晶硅）</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>产能锚点占位，尚无产量披露</t>
         </is>
@@ -2215,17 +2225,17 @@
         <f>IF(AND(ISNUMBER(V14),ISNUMBER(O14),O14&lt;&gt;0),(V14-O14)/O14,"-")</f>
         <v/>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>产能锚点占位，尚无产量披露</t>
         </is>
@@ -2344,17 +2354,17 @@
         <f>IF(AND(ISNUMBER(V15),ISNUMBER(O15),O15&lt;&gt;0),(V15-O15)/O15,"-")</f>
         <v/>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>产能锚点占位，尚无产量披露</t>
         </is>
@@ -2469,17 +2479,17 @@
         <f>IF(AND(ISNUMBER(V16),ISNUMBER(O16),O16&lt;&gt;0),(V16-O16)/O16,"-")</f>
         <v/>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>发货量口径（非产量）=硅金属+硅铁合计；硅金属 26Q1 30,533 / 26Q2 40,818 MT，硅铁 26Q1 60,674 / 26Q2 62,915 MT</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>发货量口径（shipments，非产量），与产量口径差异需注意；MT÷10000=万吨；源 Ferroglobe Q2 2026 业绩新闻稿(2026-08-04) Product Category 表</t>
         </is>
@@ -2557,6 +2567,14 @@
       </c>
       <c r="V17">
         <f>SUM(V2:V16)</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>SUM(X2:X16)</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>IF(AND(ISNUMBER(X17),ISNUMBER(P17),P17&lt;&gt;0),(X17-P17)/P17,"-")</f>
         <v/>
       </c>
     </row>
@@ -2571,7 +2589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2696,17 +2714,27 @@
           <t>26Q2同比</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>26Q3</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>26Q3同比</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>变化原因</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>FY2026指引</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -2797,17 +2825,24 @@
         <f>IF(AND(ISNUMBER(V2),ISNUMBER(O2),O2&lt;&gt;0),(V2-O2)/O2,"-")</f>
         <v/>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2025Q4 起限产，2026-01 多晶硅全面停产（反内卷）；26Q1-Q2 为实际残量非缺数</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="X2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y2">
+        <f>IF(AND(ISNUMBER(X2),ISNUMBER(P2),P2&lt;&gt;0),(X2-P2)/P2,"-")</f>
+        <v/>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-07 起复产（cnfeol 月度 7/8/9 月=3.0/4.0/4.0 万吨，Q3=11.0 万吨）；此前 2026-01 全面停产（反内卷）</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>铁合金在线口径（月度三月求和）；2026-01 起全面停产见合盛研究引述[18]；2023 年度总计=年报口径，23Q1-Q3 平台拟合</t>
         </is>
@@ -2898,17 +2933,24 @@
         <f>IF(AND(ISNUMBER(V3),ISNUMBER(O3),O3&lt;&gt;0),(V3-O3)/O3,"-")</f>
         <v/>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y3">
+        <f>IF(AND(ISNUMBER(X3),ISNUMBER(P3),P3&lt;&gt;0),(X3-P3)/P3,"-")</f>
+        <v/>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>2026-01 大规模减产后逐步恢复，颗粒硅低现金成本优先保产</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>铁合金在线口径；颗粒硅+棒状硅合计；2023 年度总计=年报口径，23Q1-Q3 平台拟合</t>
         </is>
@@ -2999,17 +3041,24 @@
         <f>IF(AND(ISNUMBER(V4),ISNUMBER(O4),O4&lt;&gt;0),(V4-O4)/O4,"-")</f>
         <v/>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X4" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Y4">
+        <f>IF(AND(ISNUMBER(X4),ISNUMBER(P4),P4&lt;&gt;0),(X4-P4)/P4,"-")</f>
+        <v/>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>低电价成本优势下开工高于行业，2026 持续复产</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>待官方披露后回填</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>铁合金在线口径，与季报披露交叉验证；2023 年度总计=年报口径，23Q1-Q3 平台拟合</t>
         </is>
@@ -3100,17 +3149,24 @@
         <f>IF(AND(ISNUMBER(V5),ISNUMBER(O5),O5&lt;&gt;0),(V5-O5)/O5,"-")</f>
         <v/>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y5">
+        <f>IF(AND(ISNUMBER(X5),ISNUMBER(P5),P5&lt;&gt;0),(X5-P5)/P5,"-")</f>
+        <v/>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>2024H2 深减后 2026 逐步恢复（楼兰等配套工业硅投产）</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>铁合金在线口径；2023 年度总计=年报口径，23Q1-Q3 平台拟合</t>
         </is>
@@ -3203,17 +3259,24 @@
         <f>IF(AND(ISNUMBER(V6),ISNUMBER(O6),O6&lt;&gt;0),(V6-O6)/O6,"-")</f>
         <v/>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <f>IF(AND(ISNUMBER(X6),ISNUMBER(P6),P6&lt;&gt;0),(X6-P6)/P6,"-")</f>
+        <v/>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2024H2 停产检修后恢复；宁夏 12.5 万吨待开</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>非上市，铁合金在线口径；2023 无年度值（仅 23Q4 实际）</t>
         </is>
@@ -3306,17 +3369,24 @@
         <f>IF(AND(ISNUMBER(V7),ISNUMBER(O7),O7&lt;&gt;0),(V7-O7)/O7,"-")</f>
         <v/>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <f>IF(AND(ISNUMBER(X7),ISNUMBER(P7),P7&lt;&gt;0),(X7-P7)/P7,"-")</f>
+        <v/>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>2025 起产能利用率为 0（350 亿在建挂账，等待行业出清）</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>铁合金在线口径；2025 年报产能利用率 0；中部合盛 20 万吨工程进度 92% 但批量延后</t>
         </is>
@@ -3409,17 +3479,24 @@
         <f>IF(AND(ISNUMBER(V8),ISNUMBER(O8),O8&lt;&gt;0),(V8-O8)/O8,"-")</f>
         <v/>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Y8">
+        <f>IF(AND(ISNUMBER(X8),ISNUMBER(P8),P8&lt;&gt;0),(X8-P8)/P8,"-")</f>
+        <v/>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>2025Q3 检修减量后恢复</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>非上市，铁合金在线口径</t>
         </is>
@@ -3512,17 +3589,24 @@
         <f>IF(AND(ISNUMBER(V9),ISNUMBER(O9),O9&lt;&gt;0),(V9-O9)/O9,"-")</f>
         <v/>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <f>IF(AND(ISNUMBER(X9),ISNUMBER(P9),P9&lt;&gt;0),(X9-P9)/P9,"-")</f>
+        <v/>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>2025Q2 起停产（低价减产）</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>非上市，铁合金在线口径；工业硅 20 万吨项目另见工业硅板块</t>
         </is>
@@ -3615,17 +3699,24 @@
         <f>IF(AND(ISNUMBER(V10),ISNUMBER(O10),O10&lt;&gt;0),(V10-O10)/O10,"-")</f>
         <v/>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <f>IF(AND(ISNUMBER(X10),ISNUMBER(P10),P10&lt;&gt;0),(X10-P10)/P10,"-")</f>
+        <v/>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>50% 开工后 2025Q3 起停产（氮气保护，1-2 周可复产）</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>非上市，铁合金在线口径；停产产能氮气保护易重启</t>
         </is>
@@ -3718,17 +3809,24 @@
         <f>IF(AND(ISNUMBER(V11),ISNUMBER(O11),O11&lt;&gt;0),(V11-O11)/O11,"-")</f>
         <v/>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y11">
+        <f>IF(AND(ISNUMBER(X11),ISNUMBER(P11),P11&lt;&gt;0),(X11-P11)/P11,"-")</f>
+        <v/>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>2025H2 起明显增产（低成本产能满负荷）</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>非上市，铁合金在线口径</t>
         </is>
@@ -3821,17 +3919,24 @@
         <f>IF(AND(ISNUMBER(V12),ISNUMBER(O12),O12&lt;&gt;0),(V12-O12)/O12,"-")</f>
         <v/>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y12">
+        <f>IF(AND(ISNUMBER(X12),ISNUMBER(P12),P12&lt;&gt;0),(X12-P12)/P12,"-")</f>
+        <v/>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>2025 控产后 2026 稳定运行</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>非上市，铁合金在线口径</t>
         </is>
@@ -3924,17 +4029,24 @@
         <f>IF(AND(ISNUMBER(V13),ISNUMBER(O13),O13&lt;&gt;0),(V13-O13)/O13,"-")</f>
         <v/>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X13" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Y13">
+        <f>IF(AND(ISNUMBER(X13),ISNUMBER(P13),P13&lt;&gt;0),(X13-P13)/P13,"-")</f>
+        <v/>
+      </c>
+      <c r="Z13" t="inlineStr">
         <is>
           <t>2025Q3 新投放量</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>铁合金在线口径；新进入者</t>
         </is>
@@ -4027,17 +4139,24 @@
         <f>IF(AND(ISNUMBER(V14),ISNUMBER(O14),O14&lt;&gt;0),(V14-O14)/O14,"-")</f>
         <v/>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X14" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="Y14">
+        <f>IF(AND(ISNUMBER(X14),ISNUMBER(P14),P14&lt;&gt;0),(X14-P14)/P14,"-")</f>
+        <v/>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>平稳运行</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>非上市，铁合金在线口径</t>
         </is>
@@ -4130,17 +4249,24 @@
         <f>IF(AND(ISNUMBER(V15),ISNUMBER(O15),O15&lt;&gt;0),(V15-O15)/O15,"-")</f>
         <v/>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <f>IF(AND(ISNUMBER(X15),ISNUMBER(P15),P15&lt;&gt;0),(X15-P15)/P15,"-")</f>
+        <v/>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>2024Q3 起停产</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>非上市，铁合金在线口径</t>
         </is>
@@ -4233,17 +4359,24 @@
         <f>IF(AND(ISNUMBER(V16),ISNUMBER(O16),O16&lt;&gt;0),(V16-O16)/O16,"-")</f>
         <v/>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <f>IF(AND(ISNUMBER(X16),ISNUMBER(P16),P16&lt;&gt;0),(X16-P16)/P16,"-")</f>
+        <v/>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>2024Q3 起停产</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>非上市，铁合金在线口径</t>
         </is>
@@ -4336,17 +4469,24 @@
         <f>IF(AND(ISNUMBER(V17),ISNUMBER(O17),O17&lt;&gt;0),(V17-O17)/O17,"-")</f>
         <v/>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y17">
+        <f>IF(AND(ISNUMBER(X17),ISNUMBER(P17),P17&lt;&gt;0),(X17-P17)/P17,"-")</f>
+        <v/>
+      </c>
+      <c r="Z17" t="inlineStr">
         <is>
           <t>2026 开工回升</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>铁合金在线口径</t>
         </is>
@@ -4439,17 +4579,24 @@
         <f>IF(AND(ISNUMBER(V18),ISNUMBER(O18),O18&lt;&gt;0),(V18-O18)/O18,"-")</f>
         <v/>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <f>IF(AND(ISNUMBER(X18),ISNUMBER(P18),P18&lt;&gt;0),(X18-P18)/P18,"-")</f>
+        <v/>
+      </c>
+      <c r="Z18" t="inlineStr">
         <is>
           <t>2024 起停产</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>非上市，铁合金在线口径</t>
         </is>
@@ -4542,17 +4689,24 @@
         <f>IF(AND(ISNUMBER(V19),ISNUMBER(O19),O19&lt;&gt;0),(V19-O19)/O19,"-")</f>
         <v/>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <f>IF(AND(ISNUMBER(X19),ISNUMBER(P19),P19&lt;&gt;0),(X19-P19)/P19,"-")</f>
+        <v/>
+      </c>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>2025 起停产</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>非上市，铁合金在线口径</t>
         </is>
@@ -4645,17 +4799,24 @@
         <f>IF(AND(ISNUMBER(V20),ISNUMBER(O20),O20&lt;&gt;0),(V20-O20)/O20,"-")</f>
         <v/>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <f>IF(AND(ISNUMBER(X20),ISNUMBER(P20),P20&lt;&gt;0),(X20-P20)/P20,"-")</f>
+        <v/>
+      </c>
+      <c r="Z20" t="inlineStr">
         <is>
           <t>2025Q2 起停产（新进入者低负荷后退出）</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>铁合金在线口径；新进入者产能锚点</t>
         </is>
@@ -4776,15 +4937,20 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>OCI 季度 IR 仅披露产能(35kMT/年)+开工率(Q1 15 个月法定检修降负荷、Q2 ~90%)，未披露分季度产量吨数</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>季度资料库（≈季后4-6周）；补海外多晶硅缺口；2026-08-18新增骨架行，数据待回填；26Q1/Q2 分季度产量吨数未在 IR 官网披露（仅产能 35kMT/年+开工率），DART 事业报告 생산실적 待人工核查</t>
         </is>
@@ -4862,6 +5028,14 @@
       </c>
       <c r="V22">
         <f>SUM(V2:V21)</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>SUM(X2:X21)</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>IF(AND(ISNUMBER(X22),ISNUMBER(P22),P22&lt;&gt;0),(X22-P22)/P22,"-")</f>
         <v/>
       </c>
     </row>
@@ -4876,7 +5050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4986,6 +5160,23 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>补录多晶硅 26Q3：铁合金在线 7/8/9 月分企业明细三月求和（全国月度 10.97/11.95/12.13 万吨，19 家全覆盖）；通威 7 月起复产（3/4/4 万吨，Q3=11.0）；东方希望 7 月起归零、弘元 9 月恢复 0.2 万吨；工业硅板块 26Q3 列已开、待合盛 10 月底经营数据公告等回填</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cnfeol 白金专栏 7/8/9 月多晶硅企业产量明细（PContentDetail/10/174251、10/175304、10/176462）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel/硅.xlsx
+++ b/excel/硅.xlsx
@@ -681,6 +681,15 @@
         <f>IF(AND(ISNUMBER(V2),ISNUMBER(O2),O2&lt;&gt;0),(V2-O2)/O2,"-")</f>
         <v/>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-10月末经营数据公告)</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <f>IF(AND(ISNUMBER(X2),ISNUMBER(P2),P2&lt;&gt;0),(X2-P2)/P2,"-")</f>
+        <v/>
+      </c>
       <c r="Z2" t="inlineStr">
         <is>
           <t>2025 主动减产挺价（-22.3%）；2026Q1 检修压产、毛利率回升至 19%；26Q2 季度经营数据公告约 8 月底披露（截至 2026-08-23 未发布）</t>
@@ -810,6 +819,15 @@
         <f>IF(AND(ISNUMBER(V3),ISNUMBER(O3),O3&lt;&gt;0),(V3-O3)/O3,"-")</f>
         <v/>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-10月末；中报未披露工业硅产量)</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <f>IF(AND(ISNUMBER(X3),ISNUMBER(P3),P3&lt;&gt;0),(X3-P3)/P3,"-")</f>
+        <v/>
+      </c>
       <c r="Z3" t="inlineStr">
         <is>
           <t>2026中报(8/24)未披露工业硅产量；经营数据公告仅有机硅基础产品Q2产71,818吨(非工业硅口径)</t>
@@ -939,6 +957,15 @@
         <f>IF(AND(ISNUMBER(V4),ISNUMBER(O4),O4&lt;&gt;0),(V4-O4)/O4,"-")</f>
         <v/>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-10月末；中报未披露工业硅产量)</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <f>IF(AND(ISNUMBER(X4),ISNUMBER(P4),P4&lt;&gt;0),(X4-P4)/P4,"-")</f>
+        <v/>
+      </c>
       <c r="Z4" t="inlineStr">
         <is>
           <t>2026中报(8/24)未披露工业硅产量(金属硅为外购原料,H1均价8,101.61元/吨)；有机硅系列H1产17.31万吨(非工业硅)</t>
@@ -1068,6 +1095,15 @@
         <f>IF(AND(ISNUMBER(V5),ISNUMBER(O5),O5&lt;&gt;0),(V5-O5)/O5,"-")</f>
         <v/>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-10月末；中报未披露工业硅产量)</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <f>IF(AND(ISNUMBER(X5),ISNUMBER(P5),P5&lt;&gt;0),(X5-P5)/P5,"-")</f>
+        <v/>
+      </c>
       <c r="Z5" t="inlineStr">
         <is>
           <t>2026中报(8/19)无任何产量披露(仅产能60万吨有机硅单体/年+分产品营收)</t>
@@ -1197,6 +1233,10 @@
         <f>IF(AND(ISNUMBER(V6),ISNUMBER(O6),O6&lt;&gt;0),(V6-O6)/O6,"-")</f>
         <v/>
       </c>
+      <c r="Y6">
+        <f>IF(AND(ISNUMBER(X6),ISNUMBER(P6),P6&lt;&gt;0),(X6-P6)/P6,"-")</f>
+        <v/>
+      </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>2026-07 调研：17 台 33MVA 炉开 12 台，月产 2 万+吨</t>
@@ -1326,6 +1366,10 @@
         <f>IF(AND(ISNUMBER(V7),ISNUMBER(O7),O7&lt;&gt;0),(V7-O7)/O7,"-")</f>
         <v/>
       </c>
+      <c r="Y7">
+        <f>IF(AND(ISNUMBER(X7),ISNUMBER(P7),P7&lt;&gt;0),(X7-P7)/P7,"-")</f>
+        <v/>
+      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>-</t>
@@ -1451,6 +1495,15 @@
         <f>IF(AND(ISNUMBER(V8),ISNUMBER(O8),O8&lt;&gt;0),(V8-O8)/O8,"-")</f>
         <v/>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-29)</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <f>IF(AND(ISNUMBER(X8),ISNUMBER(P8),P8&lt;&gt;0),(X8-P8)/P8,"-")</f>
+        <v/>
+      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>Silicon Products 分部销量口径（kt，Excl. microsilica/quartz）；2026-02 Silicones 分部出售给 Bluestar，2026 起仅 Silicon Products 分部</t>
@@ -1580,6 +1633,10 @@
         <f>IF(AND(ISNUMBER(V9),ISNUMBER(O9),O9&lt;&gt;0),(V9-O9)/O9,"-")</f>
         <v/>
       </c>
+      <c r="Y9">
+        <f>IF(AND(ISNUMBER(X9),ISNUMBER(P9),P9&lt;&gt;0),(X9-P9)/P9,"-")</f>
+        <v/>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>配套多晶硅一体化放量（计划）</t>
@@ -1709,6 +1766,10 @@
         <f>IF(AND(ISNUMBER(V10),ISNUMBER(O10),O10&lt;&gt;0),(V10-O10)/O10,"-")</f>
         <v/>
       </c>
+      <c r="Y10">
+        <f>IF(AND(ISNUMBER(X10),ISNUMBER(P10),P10&lt;&gt;0),(X10-P10)/P10,"-")</f>
+        <v/>
+      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>-</t>
@@ -1838,6 +1899,10 @@
         <f>IF(AND(ISNUMBER(V11),ISNUMBER(O11),O11&lt;&gt;0),(V11-O11)/O11,"-")</f>
         <v/>
       </c>
+      <c r="Y11">
+        <f>IF(AND(ISNUMBER(X11),ISNUMBER(P11),P11&lt;&gt;0),(X11-P11)/P11,"-")</f>
+        <v/>
+      </c>
       <c r="Z11" t="inlineStr">
         <is>
           <t>-</t>
@@ -1967,6 +2032,10 @@
         <f>IF(AND(ISNUMBER(V12),ISNUMBER(O12),O12&lt;&gt;0),(V12-O12)/O12,"-")</f>
         <v/>
       </c>
+      <c r="Y12">
+        <f>IF(AND(ISNUMBER(X12),ISNUMBER(P12),P12&lt;&gt;0),(X12-P12)/P12,"-")</f>
+        <v/>
+      </c>
       <c r="Z12" t="inlineStr">
         <is>
           <t>-</t>
@@ -2096,6 +2165,10 @@
         <f>IF(AND(ISNUMBER(V13),ISNUMBER(O13),O13&lt;&gt;0),(V13-O13)/O13,"-")</f>
         <v/>
       </c>
+      <c r="Y13">
+        <f>IF(AND(ISNUMBER(X13),ISNUMBER(P13),P13&lt;&gt;0),(X13-P13)/P13,"-")</f>
+        <v/>
+      </c>
       <c r="Z13" t="inlineStr">
         <is>
           <t>2026 逐步投产（配套新特多晶硅）</t>
@@ -2225,6 +2298,10 @@
         <f>IF(AND(ISNUMBER(V14),ISNUMBER(O14),O14&lt;&gt;0),(V14-O14)/O14,"-")</f>
         <v/>
       </c>
+      <c r="Y14">
+        <f>IF(AND(ISNUMBER(X14),ISNUMBER(P14),P14&lt;&gt;0),(X14-P14)/P14,"-")</f>
+        <v/>
+      </c>
       <c r="Z14" t="inlineStr">
         <is>
           <t>-</t>
@@ -2354,6 +2431,10 @@
         <f>IF(AND(ISNUMBER(V15),ISNUMBER(O15),O15&lt;&gt;0),(V15-O15)/O15,"-")</f>
         <v/>
       </c>
+      <c r="Y15">
+        <f>IF(AND(ISNUMBER(X15),ISNUMBER(P15),P15&lt;&gt;0),(X15-P15)/P15,"-")</f>
+        <v/>
+      </c>
       <c r="Z15" t="inlineStr">
         <is>
           <t>-</t>
@@ -2477,6 +2558,15 @@
       </c>
       <c r="W16">
         <f>IF(AND(ISNUMBER(V16),ISNUMBER(O16),O16&lt;&gt;0),(V16-O16)/O16,"-")</f>
+        <v/>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>待发布(2026-11-03)</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <f>IF(AND(ISNUMBER(X16),ISNUMBER(P16),P16&lt;&gt;0),(X16-P16)/P16,"-")</f>
         <v/>
       </c>
       <c r="Z16" t="inlineStr">
@@ -5050,7 +5140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5177,6 +5267,23 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>硅26Q3披露日历核对：合盛/Elkem/Ferroglobe及新安/兴发/东岳标待发布；多晶硅26Q3已于10/8按cnfeol月度明细入库</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Elkem 10/29、Ferroglobe 11/3披露日历；合盛及A股定期报告预约</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
